--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:54:19+00:00</t>
+    <t>2026-09-01T20:22:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:22:52+00:00</t>
+    <t>2026-09-01T21:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Verweis auf das Register, an dem die Person teilnimmt, als Library nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Notwendig, weil ResearchSubject.study nur auf ResearchStudy zeigen kann, das Modul Studie ein Register aber als Library modelliert.</t>
+    <t>Optionaler Verweis auf den Library-Katalogeintrag des Registers nach dem Profil mii-pr-studie-register des MII KDS Moduls Studie. Der verbindliche Registerbezug laeuft ueber ResearchSubject.study, das in R4 zwingend auf eine ResearchStudy zeigt.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -326,7 +326,7 @@
 </t>
   </si>
   <si>
-    <t>Register (Library nach mii-pr-studie-register)</t>
+    <t>Katalogeintrag des Registers (Library nach mii-pr-studie-register)</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:17:23+00:00</t>
+    <t>2026-09-01T21:34:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:34:57+00:00</t>
+    <t>2026-09-01T21:46:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:46:35+00:00</t>
+    <t>2026-09-02T02:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
+++ b/branches/feat/jardin-datenpunkte/StructureDefinition-mii-ex-seltene-register.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T02:40:35+00:00</t>
+    <t>2026-09-02T02:52:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
